--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D3">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3">
         <v>31</v>
